--- a/fixed_asset_ledger.xlsx
+++ b/fixed_asset_ledger.xlsx
@@ -421,7 +421,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Meridian Data Services - Fixed Asset Ledger</t>
+          <t>Copr &amp; Partners IT Services - Fixed Asset Ledger</t>
         </is>
       </c>
     </row>

--- a/fixed_asset_ledger.xlsx
+++ b/fixed_asset_ledger.xlsx
@@ -421,7 +421,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Copr &amp; Partners IT Services - Fixed Asset Ledger</t>
+          <t>Yanou &amp; Partners IT Services - Fixed Asset Ledger</t>
         </is>
       </c>
     </row>

--- a/fixed_asset_ledger.xlsx
+++ b/fixed_asset_ledger.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Asset Ledger" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fixed Asset Ledger" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -432,6 +432,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -1794,7 +1795,7 @@
         <v>450.12</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>514.88</v>
+        <v>479.88</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
